--- a/agile_documents/Unit_Test_Plan_v0.1.xlsx
+++ b/agile_documents/Unit_Test_Plan_v0.1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3DF93A8BBD052DAA/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{15EE7A82-FBFC-4319-B4B6-80C2046227A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="8_{15EE7A82-FBFC-4319-B4B6-80C2046227A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6F394EAB-7A66-4A35-B082-1D084A3D8C9D}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C3B83BB6-2AB9-4547-8541-9F6969E92BF1}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t>Actual Result</t>
   </si>
@@ -127,13 +127,43 @@
   </si>
   <si>
     <t>As the expected results, the RAG pipeline fetched the correct chunks from the indexed documents and displayed them in an easy-to-understand format.</t>
+  </si>
+  <si>
+    <t>Ensuring RAG search filters out duplicate or heavily overlapping chunks</t>
+  </si>
+  <si>
+    <t>Type a broad security query in the "RAG Knowledge Base Query" tab and examine the returned expander results.</t>
+  </si>
+  <si>
+    <t>The system should check chunk content against a set to prevent back-to-back identical or redundant text sections from rendering.</t>
+  </si>
+  <si>
+    <t>All displayed result cards should contain unique text content without repetitive paragraphs or overlapping rule sections.</t>
+  </si>
+  <si>
+    <t>As expected, the deduplication logic successfully filtered out overlapping chunks, displaying only distinct and unique rule references.</t>
+  </si>
+  <si>
+    <t>Ensuring RAG query response speed via embedding caching</t>
+  </si>
+  <si>
+    <t>Execute a security query for the first time, clear/reset, and run a subsequent query or repeat the search.</t>
+  </si>
+  <si>
+    <t>The system should utilize Streamlit's @st.cache_resource to keep the HuggingFace embedding model loaded in memory.</t>
+  </si>
+  <si>
+    <t>Subsequent searches should execute almost instantaneously without reloading model weights from scratch.</t>
+  </si>
+  <si>
+    <t>As expected, caching the embedding model eliminated initialization latency, resulting in near-instantaneous RAG query retrieval.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -159,6 +189,10 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial Unicode MS"/>
     </font>
   </fonts>
   <fills count="3">
@@ -202,11 +236,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -219,11 +250,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -539,8 +570,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF95B16C-182C-4757-B929-A728708A2DB0}">
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="1" width="7.109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34.21875" style="1" customWidth="1"/>
@@ -551,28 +582,28 @@
     <col min="7" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="2" customFormat="1" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:6" ht="15.6">
+      <c r="A1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="66" x14ac:dyDescent="0.25">
-      <c r="A2" s="7">
+    <row r="2" spans="1:6" ht="66">
+      <c r="A2" s="5">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -591,8 +622,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="66" x14ac:dyDescent="0.25">
-      <c r="A3" s="7">
+    <row r="3" spans="1:6" ht="66">
+      <c r="A3" s="5">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -611,8 +642,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="52.8" x14ac:dyDescent="0.25">
-      <c r="A4" s="7">
+    <row r="4" spans="1:6" ht="52.8">
+      <c r="A4" s="5">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -627,48 +658,88 @@
       <c r="E4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="52.8" x14ac:dyDescent="0.25">
-      <c r="A5" s="7">
+    <row r="5" spans="1:6" ht="52.8">
+      <c r="A5" s="5">
         <v>4</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="79.2" x14ac:dyDescent="0.25">
-      <c r="A6" s="7">
+    <row r="6" spans="1:6" ht="79.2">
+      <c r="A6" s="5">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="1" t="s">
         <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="79.2">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="66">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/agile_documents/Unit_Test_Plan_v0.1.xlsx
+++ b/agile_documents/Unit_Test_Plan_v0.1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3DF93A8BBD052DAA/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3df93a8bbd052daa/Desktop/Milestone 2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="8_{15EE7A82-FBFC-4319-B4B6-80C2046227A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6F394EAB-7A66-4A35-B082-1D084A3D8C9D}"/>
+  <xr:revisionPtr revIDLastSave="78" documentId="8_{15EE7A82-FBFC-4319-B4B6-80C2046227A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A5EA6406-F7DC-4098-AC7F-7E85BDA78D97}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C3B83BB6-2AB9-4547-8541-9F6969E92BF1}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
   <si>
     <t>Actual Result</t>
   </si>
@@ -157,6 +157,100 @@
   </si>
   <si>
     <t>As expected, caching the embedding model eliminated initialization latency, resulting in near-instantaneous RAG query retrieval.</t>
+  </si>
+  <si>
+    <t>Ensuring parallel multi-agent execution works correctly</t>
+  </si>
+  <si>
+    <t>Ensuring executive PDF report generation compiles properly</t>
+  </si>
+  <si>
+    <t>Ensuring SARIF compliance JSON export works seamlessly</t>
+  </si>
+  <si>
+    <t>Ensuring security letter grade scorecard calculates correctly</t>
+  </si>
+  <si>
+    <t>Input a complex code file with multiple security vulnerabilities and click the analysis button.</t>
+  </si>
+  <si>
+    <t>Run an analysis yielding findings, then click the PDF download button.</t>
+  </si>
+  <si>
+    <t>Click the SARIF export button after running an analysis on vulnerable code.</t>
+  </si>
+  <si>
+    <t>Analyze codebases with varying counts of high and medium severity vulnerabilities.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The system should utilize </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>ThreadPoolExecutor</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> to execute the Security Agent and Code Analysis Agent concurrently.</t>
+    </r>
+  </si>
+  <si>
+    <t>The system should compile findings, severities, and remediation advice into a formatted ReportLab document.</t>
+  </si>
+  <si>
+    <t>The system should map findings into industry-standard SARIF 2.1.0 schema structure with correct rule IDs and severities.</t>
+  </si>
+  <si>
+    <t>The system should compute an automated health grade (A to F) and quality gate status based on weighted severities.</t>
+  </si>
+  <si>
+    <t>Both agents should return findings simultaneously, which are then merged and deduplicated successfully.</t>
+  </si>
+  <si>
+    <r>
+      <t>A downloadable PDF file (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>code_review_report.pdf</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>) should generate successfully with correct table alignments.</t>
+    </r>
+  </si>
+  <si>
+    <t>A valid JSON/SARIF file should be downloaded, ready for CI/CD or GitHub Actions integration.</t>
+  </si>
+  <si>
+    <t>The dashboard should display a clear grade card banner reflecting the overall security posture of the uploaded file.</t>
+  </si>
+  <si>
+    <t>As expected, the multi-agent pipeline executed in parallel via threads and combined all findings without duplicates.</t>
+  </si>
+  <si>
+    <t>As expected, the ReportLab module compiled an executive PDF report containing all structured findings.</t>
+  </si>
+  <si>
+    <t>As expected, the SARIF exporter generated a valid compliance schema containing all agent findings.</t>
+  </si>
+  <si>
+    <t>As expected, the grading function accurately evaluated the findings and rendered the correct security letter grade.</t>
   </si>
 </sst>
 </file>
@@ -209,7 +303,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -232,11 +326,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFC4C7C5"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFC4C7C5"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFC4C7C5"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFC4C7C5"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -256,6 +365,12 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -271,6 +386,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -570,7 +689,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF95B16C-182C-4757-B929-A728708A2DB0}">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="1" width="7.109375" style="1" bestFit="1" customWidth="1"/>
@@ -642,7 +761,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="52.8">
+    <row r="4" spans="1:6" ht="76.8" customHeight="1">
       <c r="A4" s="5">
         <v>3</v>
       </c>
@@ -662,7 +781,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="52.8">
+    <row r="5" spans="1:6" ht="82.8" customHeight="1">
       <c r="A5" s="5">
         <v>4</v>
       </c>
@@ -682,7 +801,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="79.2">
+    <row r="6" spans="1:6" ht="99" customHeight="1">
       <c r="A6" s="5">
         <v>5</v>
       </c>
@@ -702,7 +821,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="79.2">
+    <row r="7" spans="1:6" ht="99.6" customHeight="1">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -722,7 +841,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="66">
+    <row r="8" spans="1:6" ht="89.4" customHeight="1">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -740,6 +859,86 @@
       </c>
       <c r="F8" s="4" t="s">
         <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="79.2" customHeight="1">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="83.4" customHeight="1">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="75.599999999999994" customHeight="1" thickBot="1">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="72.599999999999994" customHeight="1" thickBot="1">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>60</v>
       </c>
     </row>
   </sheetData>
